--- a/tests/input/2604131724_Sample-Class-Input/Class_Define_Template.xlsx
+++ b/tests/input/2604131724_Sample-Class-Input/Class_Define_Template.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Gasket_Group" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Bolt_Group" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Valve_Group" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Size_Selection" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -80,13 +81,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1099,13 +1103,922 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>DN</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1215,6 +2128,16 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Size_From</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Size_To</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1285,6 +2208,16 @@
       <c r="O2" t="inlineStr">
         <is>
           <t>RT1</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1502,7 +2435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="5"/>
@@ -1534,6 +2467,21 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Nominal_Size_System</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Size_From</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Size_To</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1556,6 +2504,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1578,6 +2541,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1600,6 +2578,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1622,6 +2615,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1644,6 +2652,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1666,6 +2689,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1688,6 +2726,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1710,6 +2763,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1732,6 +2800,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1754,6 +2837,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1776,6 +2874,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1798,6 +2911,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1820,6 +2948,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1842,6 +2985,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1864,6 +3022,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1886,6 +3059,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1908,6 +3096,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1930,6 +3133,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1952,6 +3170,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1974,6 +3207,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1996,6 +3244,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2018,6 +3281,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2040,6 +3318,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2062,6 +3355,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2084,6 +3392,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2106,6 +3429,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2128,6 +3466,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2150,6 +3503,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2172,6 +3540,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2194,6 +3577,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2216,6 +3614,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2238,6 +3651,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2260,6 +3688,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2282,6 +3725,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2304,6 +3762,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2326,6 +3799,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2348,6 +3836,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2370,6 +3873,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2392,6 +3910,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2414,6 +3947,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2436,6 +3984,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2458,6 +4021,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2480,6 +4058,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2502,6 +4095,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2524,6 +4132,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2546,6 +4169,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2568,6 +4206,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2590,6 +4243,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2612,6 +4280,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2634,6 +4317,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2656,6 +4354,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2678,6 +4391,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2700,6 +4428,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2722,6 +4465,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2744,6 +4502,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2766,6 +4539,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2788,6 +4576,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2810,6 +4613,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2832,6 +4650,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2854,6 +4687,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2876,6 +4724,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2898,6 +4761,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2920,6 +4798,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2942,6 +4835,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2964,6 +4872,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2986,6 +4909,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3008,6 +4946,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3030,6 +4983,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3052,6 +5020,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3074,6 +5057,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3096,6 +5094,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3118,6 +5131,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3140,6 +5168,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3162,6 +5205,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3184,6 +5242,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3206,6 +5279,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3228,6 +5316,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3250,6 +5353,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3272,6 +5390,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3294,6 +5427,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3316,6 +5464,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3338,6 +5501,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3360,6 +5538,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3382,6 +5575,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3404,6 +5612,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3426,6 +5649,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3448,6 +5686,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3470,6 +5723,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3492,6 +5760,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3514,6 +5797,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3536,6 +5834,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3558,6 +5871,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3580,6 +5908,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3602,6 +5945,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3624,6 +5982,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3646,6 +6019,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3668,6 +6056,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3690,6 +6093,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3712,6 +6130,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3734,6 +6167,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3756,6 +6204,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3778,6 +6241,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3800,6 +6278,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3822,6 +6315,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3844,6 +6352,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3866,6 +6389,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3888,6 +6426,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3910,6 +6463,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3932,6 +6500,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3954,6 +6537,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3976,6 +6574,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3998,6 +6611,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4020,6 +6648,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4042,6 +6685,21 @@
           <t>T</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4064,6 +6722,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4086,6 +6759,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4108,6 +6796,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4130,6 +6833,21 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4152,6 +6870,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4174,6 +6907,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4196,6 +6944,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4218,6 +6981,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4240,6 +7018,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4262,6 +7055,21 @@
           <t>RT</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4282,6 +7090,21 @@
       <c r="D126" t="inlineStr">
         <is>
           <t>T</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -4296,7 +7119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="5"/>
@@ -4328,6 +7151,21 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Nominal_Size_System</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Size_From</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Size_To</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4350,6 +7188,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4372,6 +7225,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4394,6 +7262,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4416,6 +7299,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4438,6 +7336,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4460,6 +7373,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4482,6 +7410,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4504,6 +7447,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4526,6 +7484,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4548,6 +7521,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4570,6 +7558,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4592,6 +7595,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4614,6 +7632,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4636,6 +7669,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4658,6 +7706,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4680,6 +7743,21 @@
           <t>SN</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4702,6 +7780,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4724,6 +7817,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4746,6 +7854,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4768,6 +7891,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4790,6 +7928,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4812,6 +7965,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4834,6 +8002,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4856,6 +8039,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4878,6 +8076,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4900,6 +8113,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4922,6 +8150,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4944,6 +8187,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4966,6 +8224,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4988,6 +8261,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5010,6 +8298,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5032,6 +8335,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5054,6 +8372,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5076,6 +8409,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5098,6 +8446,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5120,6 +8483,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5142,6 +8520,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5164,6 +8557,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5186,6 +8594,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5208,6 +8631,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5230,6 +8668,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5252,6 +8705,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5274,6 +8742,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5296,6 +8779,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5318,6 +8816,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5340,6 +8853,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5362,6 +8890,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5384,6 +8927,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5406,6 +8964,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5428,6 +9001,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5450,6 +9038,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5472,6 +9075,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5494,6 +9112,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5516,6 +9149,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5538,6 +9186,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5560,6 +9223,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5582,6 +9260,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5604,6 +9297,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5626,6 +9334,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5648,6 +9371,21 @@
           <t>RD</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5668,6 +9406,21 @@
       <c r="D62" t="inlineStr">
         <is>
           <t>RD</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>NPS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>
